--- a/sample/input-mixed.xlsx
+++ b/sample/input-mixed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,6 +508,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30094410887</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18 Oak 408x960 CAD-944108</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30034643897</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18 Anth 338x666 CAD-346438</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
